--- a/case_studies/backbone/networks/new/hydrogenPipelineOnshore.xlsx
+++ b/case_studies/backbone/networks/new/hydrogenPipelineOnshore.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\case_1\networks\new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\backbone\networks\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D9530A-43C2-4E96-94EA-1686BEADED54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3769C1-3DF2-4526-8CF5-1B1466D1CC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -843,8 +843,8 @@
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="27" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="42" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="26" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="41" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -881,22 +881,22 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -904,25 +904,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -930,25 +930,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -956,25 +956,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -982,25 +982,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1008,25 +1008,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1034,22 +1034,22 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>

--- a/case_studies/backbone/networks/new/hydrogenPipelineOnshore.xlsx
+++ b/case_studies/backbone/networks/new/hydrogenPipelineOnshore.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3769C1-3DF2-4526-8CF5-1B1466D1CC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="distances" sheetId="5" r:id="rId1"/>
